--- a/5/search/FY3_Missile3_results/top10_solutions.xlsx
+++ b/5/search/FY3_Missile3_results/top10_solutions.xlsx
@@ -490,28 +490,28 @@
         <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>120.4</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="I2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="J2" t="n">
         <v>700</v>
@@ -525,139 +525,139 @@
         <v>81</v>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6420.495842028141</v>
+        <v>6431.759123511038</v>
       </c>
       <c r="F3" t="n">
-        <v>-345.0937404802698</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6446.7768321549</v>
+        <v>6453.347079686589</v>
       </c>
       <c r="I3" t="n">
-        <v>-179.1620992602867</v>
+        <v>-137.6791889552907</v>
       </c>
       <c r="J3" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B4" t="n">
-        <v>128.8</v>
+        <v>136</v>
       </c>
       <c r="C4" t="n">
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>6000</v>
+        <v>6213.408740379738</v>
       </c>
       <c r="F4" t="n">
-        <v>-424</v>
+        <v>-288.384852245892</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6000</v>
+        <v>6224.079177398726</v>
       </c>
       <c r="I4" t="n">
-        <v>-166.4</v>
+        <v>-152.8040948581866</v>
       </c>
       <c r="J4" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126</v>
+        <v>112.5</v>
       </c>
       <c r="B5" t="n">
-        <v>114.8</v>
+        <v>122</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>4380.534072883778</v>
+        <v>5066.252425029181</v>
       </c>
       <c r="F5" t="n">
-        <v>-770.9963770981449</v>
+        <v>-745.7339406724604</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>3908.189844141547</v>
+        <v>4786.128152537935</v>
       </c>
       <c r="I5" t="n">
-        <v>-120.8703204184371</v>
+        <v>-69.45412287419856</v>
       </c>
       <c r="J5" t="n">
-        <v>459.9</v>
+        <v>523.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126</v>
+        <v>94.5</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>4420.033241837833</v>
+        <v>5805.421442594945</v>
       </c>
       <c r="F6" t="n">
-        <v>-825.3623191201414</v>
+        <v>-527.6450123418426</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>3867.044876481074</v>
+        <v>5776.234658984186</v>
       </c>
       <c r="I6" t="n">
-        <v>-64.23913081219098</v>
+        <v>-156.791764193119</v>
       </c>
       <c r="J6" t="n">
-        <v>459.9</v>
+        <v>655.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -665,174 +665,174 @@
         <v>81</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6429.256172070393</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="F7" t="n">
-        <v>-289.7831934069422</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6444.586749644336</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="I7" t="n">
-        <v>-192.9897360286188</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="J7" t="n">
-        <v>695.1</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81</v>
+        <v>85.5</v>
       </c>
       <c r="B8" t="n">
-        <v>114.8</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6431.008238078844</v>
+        <v>6207.13201272151</v>
       </c>
       <c r="F8" t="n">
-        <v>-278.7210839922764</v>
+        <v>-368.1382389445425</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6448.966914665463</v>
+        <v>6224.393013781636</v>
       </c>
       <c r="I8" t="n">
-        <v>-165.3344624919546</v>
+        <v>-148.8164255232544</v>
       </c>
       <c r="J8" t="n">
-        <v>695.1</v>
+        <v>680.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B9" t="n">
-        <v>120.4</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>5623.305808183124</v>
+        <v>6000</v>
       </c>
       <c r="F9" t="n">
-        <v>-621.6464758469083</v>
+        <v>-408</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>5547.966969819749</v>
+        <v>6000</v>
       </c>
       <c r="I9" t="n">
-        <v>-145.9757710162899</v>
+        <v>-192</v>
       </c>
       <c r="J9" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>103.6</v>
+        <v>128</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5231.660145186131</v>
+        <v>6000</v>
       </c>
       <c r="F10" t="n">
-        <v>-635.2930778837299</v>
+        <v>-440</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>5071.589342099908</v>
+        <v>6000</v>
       </c>
       <c r="I10" t="n">
-        <v>-142.6458024428404</v>
+        <v>-184</v>
       </c>
       <c r="J10" t="n">
-        <v>577.5</v>
+        <v>680.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B11" t="n">
-        <v>120.4</v>
+        <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>5255.887077545127</v>
+        <v>6000</v>
       </c>
       <c r="F11" t="n">
-        <v>-709.8559087612698</v>
+        <v>-456</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>5069.858846931409</v>
+        <v>6000</v>
       </c>
       <c r="I11" t="n">
-        <v>-137.3198859515873</v>
+        <v>-138</v>
       </c>
       <c r="J11" t="n">
-        <v>577.5</v>
+        <v>655.9</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
